--- a/diseases/d183/2010-2014.xlsx
+++ b/diseases/d183/2010-2014.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4543,6 +4673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4688,6 +4823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4833,6 +4973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4978,6 +5123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5123,6 +5273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5268,6 +5423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5413,6 +5573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6002,6 +6167,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6739,6 +6909,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7624,6 +7799,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8361,6 +8541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9246,6 +9431,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9983,6 +10173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10720,6 +10915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11457,6 +11657,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12342,6 +12547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13079,6 +13289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13816,6 +14031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14701,6 +14921,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15438,6 +15663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16323,6 +16553,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17060,6 +17295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17797,6 +18037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18682,6 +18927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19419,6 +19669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20156,6 +20411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20893,6 +21153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21778,6 +22043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22515,6 +22785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23400,6 +23675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24137,6 +24417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24874,6 +25159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25759,6 +26049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26494,6 +26789,11 @@
       <c r="S177" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">

--- a/diseases/d183/2010-2014.xlsx
+++ b/diseases/d183/2010-2014.xlsx
@@ -5726,28 +5726,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5874,28 +5888,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6022,28 +6050,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6320,28 +6362,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6468,28 +6524,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6616,28 +6686,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6764,28 +6848,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7062,28 +7160,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7210,28 +7322,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7358,28 +7484,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7506,28 +7646,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7654,28 +7808,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -7952,28 +8120,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8100,28 +8282,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8248,28 +8444,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8396,28 +8606,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8694,28 +8918,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8842,28 +9080,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -8990,28 +9242,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9138,28 +9404,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9286,28 +9566,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9584,28 +9878,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9732,28 +10040,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -9880,28 +10202,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10028,28 +10364,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -10326,28 +10676,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10474,28 +10838,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10622,28 +11000,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -10770,28 +11162,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -11068,28 +11474,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11216,28 +11636,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11364,28 +11798,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11512,28 +11960,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -11810,28 +12272,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -11958,28 +12434,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12106,28 +12596,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -12254,28 +12758,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12402,28 +12920,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12700,28 +13232,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -12848,28 +13394,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -12996,28 +13556,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -13144,28 +13718,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -13442,28 +14030,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13590,28 +14192,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13738,28 +14354,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -13886,28 +14516,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -14184,28 +14828,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14332,28 +14990,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14480,28 +15152,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14628,28 +15314,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -14776,28 +15476,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -15074,28 +15788,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15222,28 +15950,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15370,28 +16112,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15518,28 +16274,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -15816,28 +16586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -15964,28 +16748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16112,28 +16910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -16260,28 +17072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -16408,28 +17234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16706,28 +17546,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -16854,28 +17708,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17002,28 +17870,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17150,28 +18032,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -17448,28 +18344,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17596,28 +18506,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -17744,28 +18668,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -17892,28 +18830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -18190,28 +19142,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18338,28 +19304,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -18486,28 +19466,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -18634,28 +19628,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -18782,28 +19790,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -19080,28 +20102,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -19228,28 +20264,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -19376,28 +20426,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -19524,28 +20588,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -19822,28 +20900,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -19970,28 +21062,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20118,28 +21224,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -20266,28 +21386,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -20564,28 +21698,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -20712,28 +21860,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -20860,28 +22022,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21008,28 +22184,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -21306,28 +22496,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -21454,28 +22658,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -21602,28 +22820,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -21750,28 +22982,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -21898,28 +23144,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -22196,28 +23456,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22344,28 +23618,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -22492,28 +23780,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -22640,28 +23942,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -22938,28 +24254,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -23086,28 +24416,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -23234,28 +24578,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -23382,28 +24740,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -23530,28 +24902,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -23828,28 +25214,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -23976,28 +25376,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -24124,28 +25538,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -24272,28 +25700,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -24570,28 +26012,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -24718,28 +26174,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -24866,28 +26336,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -25014,28 +26498,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -25312,28 +26810,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -25460,28 +26972,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -25608,28 +27134,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -25756,28 +27296,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -25904,28 +27458,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -26202,28 +27770,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -26350,28 +27932,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -26498,28 +28094,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -26646,28 +28256,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -26944,28 +28568,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -27092,28 +28730,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -27240,28 +28892,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -27388,28 +29054,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">

--- a/diseases/d183/2010-2014.xlsx
+++ b/diseases/d183/2010-2014.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3918,11 +3603,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,22 +3615,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4068,11 +3738,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4085,22 +3750,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4218,11 +3873,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4235,22 +3885,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4368,11 +4008,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4385,22 +4020,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4518,11 +4143,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4535,22 +4155,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4668,11 +4278,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4685,22 +4290,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4818,11 +4413,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4835,22 +4425,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4968,11 +4548,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4985,22 +4560,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5118,11 +4683,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5135,22 +4695,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5268,11 +4818,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5285,22 +4830,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5418,11 +4953,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5435,22 +4965,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5568,11 +5088,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5585,22 +5100,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6204,11 +5709,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6221,22 +5721,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -7002,11 +6492,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7019,22 +6504,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7962,11 +7437,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7979,22 +7449,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8760,11 +8220,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8777,22 +8232,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9720,11 +9165,6 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9737,22 +9177,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10518,11 +9948,6 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10535,22 +9960,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11316,11 +10731,6 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11333,22 +10743,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -12114,11 +11514,6 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12131,22 +11526,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -13074,11 +12459,6 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13091,22 +12471,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13872,11 +13242,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13889,22 +13254,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14670,11 +14025,6 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14687,22 +14037,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15630,11 +14970,6 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15647,22 +14982,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -16428,11 +15753,6 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16445,22 +15765,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -17388,11 +16698,6 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17405,22 +16710,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -18186,11 +17481,6 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18203,22 +17493,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18984,11 +18264,6 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19001,22 +18276,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -19944,11 +19209,6 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19961,22 +19221,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -20742,11 +19992,6 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20759,22 +20004,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -21540,11 +20775,6 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21557,22 +20787,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -22338,11 +21558,6 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22355,22 +21570,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -23298,11 +22503,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23315,22 +22515,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -24096,11 +23286,6 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24113,22 +23298,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -25056,11 +24231,6 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25073,22 +24243,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -25854,11 +25014,6 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25871,22 +25026,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -26652,11 +25797,6 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26669,22 +25809,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -27612,11 +26742,6 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27629,22 +26754,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -28410,11 +27525,6 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28427,22 +27537,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>

--- a/diseases/d183/2010-2014.xlsx
+++ b/diseases/d183/2010-2014.xlsx
@@ -5220,17 +5220,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -5238,7 +5236,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5248,12 +5246,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -5263,11 +5256,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5382,17 +5370,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -5400,7 +5386,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5410,12 +5396,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -5425,11 +5406,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5544,17 +5520,15 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -5562,7 +5536,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5572,12 +5546,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -5587,11 +5556,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5841,17 +5805,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -5859,7 +5821,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5869,12 +5831,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -5884,11 +5841,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6003,17 +5955,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -6021,7 +5971,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6031,12 +5981,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6046,11 +5991,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6165,17 +6105,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -6183,7 +6121,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6193,12 +6131,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -6208,11 +6141,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6327,17 +6255,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -6345,7 +6271,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6355,12 +6281,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -6370,11 +6291,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6624,17 +6540,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -6642,7 +6556,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6652,12 +6566,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6667,11 +6576,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6786,17 +6690,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -6804,7 +6706,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6814,12 +6716,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -6829,11 +6726,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6948,17 +6840,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -6966,7 +6856,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6976,12 +6866,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -6991,11 +6876,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7110,17 +6990,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -7128,7 +7006,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7138,12 +7016,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -7153,11 +7026,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7272,17 +7140,15 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -7290,7 +7156,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7300,12 +7166,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -7315,11 +7176,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7569,17 +7425,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -7587,7 +7441,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7597,12 +7451,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -7612,11 +7461,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7731,17 +7575,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -7749,7 +7591,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -7759,12 +7601,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -7774,11 +7611,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7893,17 +7725,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -7911,7 +7741,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7921,12 +7751,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -7936,11 +7761,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8055,17 +7875,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -8073,7 +7891,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8083,12 +7901,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -8098,11 +7911,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8352,17 +8160,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -8370,7 +8176,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8380,12 +8186,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -8395,11 +8196,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8514,17 +8310,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -8532,7 +8326,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8542,12 +8336,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -8557,11 +8346,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8676,17 +8460,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -8694,7 +8476,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8704,12 +8486,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -8719,11 +8496,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8838,17 +8610,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -8856,7 +8626,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -8866,12 +8636,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -8881,11 +8646,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9000,17 +8760,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -9018,7 +8776,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9028,12 +8786,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -9043,11 +8796,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9297,17 +9045,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -9315,7 +9061,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9325,12 +9071,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -9340,11 +9081,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9459,17 +9195,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -9477,7 +9211,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9487,12 +9221,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -9502,11 +9231,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9621,17 +9345,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -9639,7 +9361,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9649,12 +9371,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -9664,11 +9381,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9783,17 +9495,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -9801,7 +9511,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -9811,12 +9521,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -9826,11 +9531,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10080,17 +9780,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -10098,7 +9796,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10108,12 +9806,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10123,11 +9816,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10242,17 +9930,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -10260,7 +9946,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10270,12 +9956,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -10285,11 +9966,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10404,17 +10080,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -10422,7 +10096,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10432,12 +10106,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -10447,11 +10116,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10566,17 +10230,15 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -10584,7 +10246,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10594,12 +10256,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -10609,11 +10266,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10863,17 +10515,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -10881,7 +10531,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -10891,12 +10541,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -10906,11 +10551,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11025,17 +10665,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -11043,7 +10681,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11053,12 +10691,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11068,11 +10701,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11187,17 +10815,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -11205,7 +10831,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11215,12 +10841,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -11230,11 +10851,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11349,17 +10965,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -11367,7 +10981,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11377,12 +10991,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -11392,11 +11001,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11646,17 +11250,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -11664,7 +11266,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11674,12 +11276,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -11689,11 +11286,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11808,17 +11400,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -11826,7 +11416,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11836,12 +11426,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -11851,11 +11436,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11970,17 +11550,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -11988,7 +11566,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11998,12 +11576,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -12013,11 +11586,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12132,17 +11700,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -12150,7 +11716,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12160,12 +11726,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -12175,11 +11736,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12294,17 +11850,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -12312,7 +11866,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12322,12 +11876,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -12337,11 +11886,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12591,17 +12135,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -12609,7 +12151,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12619,12 +12161,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -12634,11 +12171,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12753,17 +12285,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -12771,7 +12301,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12781,12 +12311,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -12796,11 +12321,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12915,17 +12435,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -12933,7 +12451,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -12943,12 +12461,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -12958,11 +12471,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13077,17 +12585,15 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -13095,7 +12601,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13105,12 +12611,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -13120,11 +12621,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13374,17 +12870,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -13392,7 +12886,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13402,12 +12896,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -13417,11 +12906,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13536,17 +13020,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -13554,7 +13036,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13564,12 +13046,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -13579,11 +13056,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13698,17 +13170,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -13716,7 +13186,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13726,12 +13196,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -13741,11 +13206,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13860,17 +13320,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -13878,7 +13336,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13888,12 +13346,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -13903,11 +13356,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14157,17 +13605,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -14175,7 +13621,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14185,12 +13631,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -14200,11 +13641,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14319,17 +13755,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -14337,7 +13771,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14347,12 +13781,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -14362,11 +13791,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14481,17 +13905,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -14499,7 +13921,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14509,12 +13931,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -14524,11 +13941,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14643,17 +14055,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -14661,7 +14071,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -14671,12 +14081,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -14686,11 +14091,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14805,17 +14205,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -14823,7 +14221,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -14833,12 +14231,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -14848,11 +14241,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15102,17 +14490,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -15120,7 +14506,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15130,12 +14516,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -15145,11 +14526,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15264,17 +14640,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -15282,7 +14656,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15292,12 +14666,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15307,11 +14676,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15426,17 +14790,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -15444,7 +14806,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -15454,12 +14816,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -15469,11 +14826,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15588,17 +14940,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -15606,7 +14956,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -15616,12 +14966,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -15631,11 +14976,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15885,17 +15225,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -15903,7 +15241,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -15913,12 +15251,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -15928,11 +15261,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16047,17 +15375,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -16065,7 +15391,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16075,12 +15401,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16090,11 +15411,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16209,17 +15525,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -16227,7 +15541,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -16237,12 +15551,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -16252,11 +15561,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16371,17 +15675,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -16389,7 +15691,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -16399,12 +15701,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -16414,11 +15711,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16533,17 +15825,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -16551,7 +15841,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -16561,12 +15851,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -16576,11 +15861,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16830,17 +16110,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -16848,7 +16126,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -16858,12 +16136,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -16873,11 +16146,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16992,17 +16260,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -17010,7 +16276,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17020,12 +16286,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -17035,11 +16296,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17154,17 +16410,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -17172,7 +16426,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -17182,12 +16436,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -17197,11 +16446,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17316,17 +16560,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -17334,7 +16576,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -17344,12 +16586,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -17359,11 +16596,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17613,17 +16845,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -17631,7 +16861,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17641,12 +16871,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -17656,11 +16881,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17775,17 +16995,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -17793,7 +17011,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -17803,12 +17021,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -17818,11 +17031,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -17937,17 +17145,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -17955,7 +17161,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -17965,12 +17171,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -17980,11 +17181,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18099,17 +17295,15 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -18117,7 +17311,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -18127,12 +17321,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -18142,11 +17331,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18396,17 +17580,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -18414,7 +17596,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18424,12 +17606,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -18439,11 +17616,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18558,17 +17730,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -18576,7 +17746,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18586,12 +17756,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -18601,11 +17766,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18720,17 +17880,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -18738,7 +17896,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -18748,12 +17906,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -18763,11 +17916,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -18882,17 +18030,15 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -18900,7 +18046,7 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -18910,12 +18056,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
@@ -18925,11 +18066,6 @@
       </c>
       <c r="AT122" t="n">
         <v>1</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19044,17 +18180,15 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -19062,7 +18196,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -19072,12 +18206,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -19087,11 +18216,6 @@
       </c>
       <c r="AT123" t="n">
         <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19341,17 +18465,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -19359,7 +18481,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -19369,12 +18491,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -19384,11 +18501,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19503,17 +18615,15 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -19521,7 +18631,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -19531,12 +18641,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -19546,11 +18651,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19665,17 +18765,15 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -19683,7 +18781,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -19693,12 +18791,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -19708,11 +18801,6 @@
       </c>
       <c r="AT127" t="n">
         <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19827,17 +18915,15 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -19845,7 +18931,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -19855,12 +18941,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
@@ -19870,11 +18951,6 @@
       </c>
       <c r="AT128" t="n">
         <v>1</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20124,17 +19200,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -20142,7 +19216,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20152,12 +19226,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -20167,11 +19236,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20286,17 +19350,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -20304,7 +19366,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -20314,12 +19376,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -20329,11 +19386,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20448,17 +19500,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -20466,7 +19516,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20476,12 +19526,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -20491,11 +19536,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20610,17 +19650,15 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -20628,7 +19666,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -20638,12 +19676,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
@@ -20653,11 +19686,6 @@
       </c>
       <c r="AT133" t="n">
         <v>1</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20907,17 +19935,15 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -20925,7 +19951,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -20935,12 +19961,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -20950,11 +19971,6 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21069,17 +20085,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -21087,7 +20101,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -21097,12 +20111,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -21112,11 +20121,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21231,17 +20235,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -21249,7 +20251,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -21259,12 +20261,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -21274,11 +20271,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21393,17 +20385,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -21411,7 +20401,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -21421,12 +20411,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -21436,11 +20421,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21690,17 +20670,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -21708,7 +20686,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -21718,12 +20696,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -21733,11 +20706,6 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21852,17 +20820,15 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -21870,7 +20836,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -21880,12 +20846,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -21895,11 +20856,6 @@
       </c>
       <c r="AT141" t="n">
         <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22014,17 +20970,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -22032,7 +20986,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -22042,12 +20996,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -22057,11 +21006,6 @@
       </c>
       <c r="AT142" t="n">
         <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22176,17 +21120,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -22194,7 +21136,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -22204,12 +21146,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -22219,11 +21156,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22338,17 +21270,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -22356,7 +21286,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -22366,12 +21296,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
@@ -22381,11 +21306,6 @@
       </c>
       <c r="AT144" t="n">
         <v>1</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22635,17 +21555,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -22653,7 +21571,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -22663,12 +21581,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -22678,11 +21591,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22797,17 +21705,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -22815,7 +21721,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -22825,12 +21731,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -22840,11 +21741,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -22959,17 +21855,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -22977,7 +21871,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -22987,12 +21881,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -23002,11 +21891,6 @@
       </c>
       <c r="AT148" t="n">
         <v>1</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23121,17 +22005,15 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -23139,7 +22021,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -23149,12 +22031,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -23164,11 +22041,6 @@
       </c>
       <c r="AT149" t="n">
         <v>1</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23418,17 +22290,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -23436,7 +22306,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -23446,12 +22316,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -23461,11 +22326,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23580,17 +22440,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -23598,7 +22456,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -23608,12 +22466,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -23623,11 +22476,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23742,17 +22590,15 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -23760,7 +22606,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -23770,12 +22616,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -23785,11 +22626,6 @@
       </c>
       <c r="AT153" t="n">
         <v>1</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -23904,17 +22740,15 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -23922,7 +22756,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -23932,12 +22766,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -23947,11 +22776,6 @@
       </c>
       <c r="AT154" t="n">
         <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24066,17 +22890,15 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -24084,7 +22906,7 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -24094,12 +22916,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
@@ -24109,11 +22926,6 @@
       </c>
       <c r="AT155" t="n">
         <v>1</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24363,17 +23175,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -24381,7 +23191,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -24391,12 +23201,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -24406,11 +23211,6 @@
       </c>
       <c r="AT157" t="n">
         <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24525,17 +23325,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -24543,7 +23341,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -24553,12 +23351,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -24568,11 +23361,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -24687,17 +23475,15 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -24705,7 +23491,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -24715,12 +23501,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -24730,11 +23511,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24849,17 +23625,15 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -24867,7 +23641,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -24877,12 +23651,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -24892,11 +23661,6 @@
       </c>
       <c r="AT160" t="n">
         <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25146,17 +23910,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -25164,7 +23926,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -25174,12 +23936,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -25189,11 +23946,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25308,17 +24060,15 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -25326,7 +24076,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -25336,12 +24086,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -25351,11 +24096,6 @@
       </c>
       <c r="AT163" t="n">
         <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25470,17 +24210,15 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -25488,7 +24226,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -25498,12 +24236,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -25513,11 +24246,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25632,17 +24360,15 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -25650,7 +24376,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -25660,12 +24386,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -25675,11 +24396,6 @@
       </c>
       <c r="AT165" t="n">
         <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -25929,17 +24645,15 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -25947,7 +24661,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -25957,12 +24671,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -25972,11 +24681,6 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26091,17 +24795,15 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -26109,7 +24811,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -26119,12 +24821,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -26134,11 +24831,6 @@
       </c>
       <c r="AT168" t="n">
         <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26253,17 +24945,15 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -26271,7 +24961,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -26281,12 +24971,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -26296,11 +24981,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26415,17 +25095,15 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -26433,7 +25111,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -26443,12 +25121,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -26458,11 +25131,6 @@
       </c>
       <c r="AT170" t="n">
         <v>1</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26577,17 +25245,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -26595,7 +25261,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -26605,12 +25271,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -26620,11 +25281,6 @@
       </c>
       <c r="AT171" t="n">
         <v>1</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -26874,17 +25530,15 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -26892,7 +25546,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -26902,12 +25556,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
@@ -26917,11 +25566,6 @@
       </c>
       <c r="AT173" t="n">
         <v>1</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -27036,17 +25680,15 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -27054,7 +25696,7 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -27064,12 +25706,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
@@ -27079,11 +25716,6 @@
       </c>
       <c r="AT174" t="n">
         <v>1</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27198,17 +25830,15 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -27216,7 +25846,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -27226,12 +25856,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -27241,11 +25866,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -27360,17 +25980,15 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -27378,7 +25996,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -27388,12 +26006,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -27403,11 +26016,6 @@
       </c>
       <c r="AT176" t="n">
         <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -27657,17 +26265,15 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -27675,7 +26281,7 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -27685,12 +26291,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
@@ -27700,11 +26301,6 @@
       </c>
       <c r="AT178" t="n">
         <v>1</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -27819,17 +26415,15 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -27837,7 +26431,7 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -27847,12 +26441,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
@@ -27862,11 +26451,6 @@
       </c>
       <c r="AT179" t="n">
         <v>1</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -27981,17 +26565,15 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -27999,7 +26581,7 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -28009,12 +26591,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
@@ -28024,11 +26601,6 @@
       </c>
       <c r="AT180" t="n">
         <v>1</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -28143,17 +26715,15 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>HOLD_JP_a39bc978e63a839d9c74c6e7f9c0</t>
@@ -28161,7 +26731,7 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -28171,12 +26741,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
@@ -28186,11 +26751,6 @@
       </c>
       <c r="AT181" t="n">
         <v>1</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>

--- a/diseases/d183/2010-2014.xlsx
+++ b/diseases/d183/2010-2014.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3603,6 +3918,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3615,12 +3935,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3738,6 +4068,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3750,12 +4085,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3873,6 +4218,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3885,12 +4235,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4008,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4020,12 +4385,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4143,6 +4518,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4155,12 +4535,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4278,6 +4668,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4290,12 +4685,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4413,6 +4818,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4425,12 +4835,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4548,6 +4968,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4560,12 +4985,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4683,6 +5118,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4695,12 +5135,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4818,6 +5268,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4830,12 +5285,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -4953,6 +5418,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4965,12 +5435,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5088,6 +5568,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5100,12 +5585,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5673,6 +6168,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5685,12 +6185,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6408,6 +6918,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6420,12 +6935,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7293,6 +7818,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7305,12 +7835,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8028,6 +8568,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8040,12 +8585,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8913,6 +9468,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8925,12 +9485,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9648,6 +10218,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9660,12 +10235,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10383,6 +10968,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10395,12 +10985,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11118,6 +11718,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11130,12 +11735,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12003,6 +12618,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12015,12 +12635,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12738,6 +13368,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12750,12 +13385,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13473,6 +14118,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13485,12 +14135,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14358,6 +15018,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14370,12 +15035,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15093,6 +15768,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15105,12 +15785,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15978,6 +16668,11 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15990,12 +16685,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16713,6 +17418,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16725,12 +17435,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17448,6 +18168,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17460,12 +18185,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18333,6 +19068,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18345,12 +19085,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19068,6 +19818,11 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19080,12 +19835,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -19803,6 +20568,11 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19815,12 +20585,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -20538,6 +21318,11 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20550,12 +21335,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21423,6 +22218,11 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21435,12 +22235,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22158,6 +22968,11 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22170,12 +22985,22 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23043,6 +23868,11 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23055,12 +23885,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -23778,6 +24618,11 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23790,12 +24635,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -24513,6 +25368,11 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24525,12 +25385,22 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -25398,6 +26268,11 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25410,12 +26285,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -26133,6 +27018,11 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26145,12 +27035,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
